--- a/artfynd/A 11145-2026 artfynd.xlsx
+++ b/artfynd/A 11145-2026 artfynd.xlsx
@@ -675,39 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132618831</v>
+        <v>132618810</v>
       </c>
       <c r="B2" t="n">
-        <v>8444</v>
+        <v>91939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520493</v>
+        <v>520542</v>
       </c>
       <c r="R2" t="n">
-        <v>6511189</v>
+        <v>6511184</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,41 +780,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132618810</v>
+        <v>132618831</v>
       </c>
       <c r="B3" t="n">
-        <v>91939</v>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520542</v>
+        <v>520493</v>
       </c>
       <c r="R3" t="n">
-        <v>6511184</v>
+        <v>6511189</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 11145-2026 artfynd.xlsx
+++ b/artfynd/A 11145-2026 artfynd.xlsx
@@ -675,41 +675,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132618810</v>
+        <v>132618831</v>
       </c>
       <c r="B2" t="n">
-        <v>91939</v>
+        <v>8444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520542</v>
+        <v>520493</v>
       </c>
       <c r="R2" t="n">
-        <v>6511184</v>
+        <v>6511189</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,39 +778,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132618831</v>
+        <v>132618810</v>
       </c>
       <c r="B3" t="n">
-        <v>8444</v>
+        <v>91939</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520493</v>
+        <v>520542</v>
       </c>
       <c r="R3" t="n">
-        <v>6511189</v>
+        <v>6511184</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 11145-2026 artfynd.xlsx
+++ b/artfynd/A 11145-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,39 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132618831</v>
+        <v>132618810</v>
       </c>
       <c r="B2" t="n">
-        <v>8444</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520493</v>
+        <v>520542</v>
       </c>
       <c r="R2" t="n">
-        <v>6511189</v>
+        <v>6511184</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,41 +780,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132618810</v>
+        <v>132618890</v>
       </c>
       <c r="B3" t="n">
-        <v>91939</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520542</v>
+        <v>520854</v>
       </c>
       <c r="R3" t="n">
-        <v>6511184</v>
+        <v>6511257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +867,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,6 +882,109 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132618831</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kopparfall, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520493</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6511189</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tjällmo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
